--- a/data/arbre.xlsx
+++ b/data/arbre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B45984\Desktop\Local\Personnel\Arbre généalogique\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B45984\Desktop\Local\Personnel\Arbre généalogique\projet github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514FE681-7684-452A-BFE9-6F2CC25E63A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4BCA5B-BD23-4370-A06A-8D86A302DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0DE5C9FF-EC24-4A3C-A571-D974C85EACB9}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{0DE5C9FF-EC24-4A3C-A571-D974C85EACB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2038,6 +2038,9 @@
       </c>
     </row>
     <row r="14" spans="1:14">
+      <c r="B14">
+        <v>11</v>
+      </c>
       <c r="C14" t="s">
         <v>96</v>
       </c>
@@ -2067,6 +2070,9 @@
       </c>
     </row>
     <row r="15" spans="1:14">
+      <c r="B15">
+        <v>22</v>
+      </c>
       <c r="C15" t="s">
         <v>105</v>
       </c>
@@ -2096,6 +2102,9 @@
       </c>
     </row>
     <row r="16" spans="1:14">
+      <c r="B16">
+        <v>44</v>
+      </c>
       <c r="C16" t="s">
         <v>113</v>
       </c>
@@ -2116,6 +2125,9 @@
       </c>
     </row>
     <row r="17" spans="1:14">
+      <c r="B17">
+        <v>88</v>
+      </c>
       <c r="C17" t="s">
         <v>119</v>
       </c>
